--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1285,7 +1285,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260619134041</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1306,7 +1306,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260619134042</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1731,7 +1731,7 @@
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260420150251</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260619134043</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.authority</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
